--- a/esercitazione_01/SDO.xlsx
+++ b/esercitazione_01/SDO.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>id_soggetto</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>P03</t>
+  </si>
+  <si>
+    <t>V30.00</t>
+  </si>
+  <si>
+    <t>P05</t>
   </si>
 </sst>
 </file>
@@ -397,18 +403,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="17.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,7 +461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -475,7 +481,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -492,7 +498,7 @@
         <v>25082</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -506,7 +512,7 @@
         <v>41005</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -520,6 +526,20 @@
         <v>39891</v>
       </c>
       <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>20221112</v>
+      </c>
+      <c r="C6">
+        <v>20221114</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
